--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DDV_HRM-2031-0440/Panel 02/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DDV_HRM-2031-0440/Panel 02/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,23 +456,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Pad Pos 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.85263</v>
+        <v>16.7843</v>
       </c>
       <c r="D2" t="n">
-        <v>16.58768</v>
+        <v>16.45542</v>
       </c>
       <c r="E2" t="n">
-        <v>16.68002</v>
+        <v>16.62977</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41.46783</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05065</v>
+        <v>0.05009</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82728</v>
+        <v>1.80216</v>
       </c>
     </row>
     <row r="3">
@@ -482,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.90183</v>
+        <v>16.73611</v>
       </c>
       <c r="D3" t="n">
-        <v>16.75245</v>
+        <v>16.47637</v>
       </c>
       <c r="E3" t="n">
-        <v>16.52343</v>
+        <v>16.73493</v>
       </c>
       <c r="F3" t="n">
-        <v>43.346</v>
+        <v>41.5178</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.04926</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8297</v>
+        <v>1.82197</v>
       </c>
     </row>
     <row r="4">
@@ -506,25 +509,23 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="C4" t="n">
+        <v>16.95956</v>
       </c>
       <c r="D4" t="n">
-        <v>16.57048</v>
+        <v>16.50206</v>
       </c>
       <c r="E4" t="n">
-        <v>16.56524</v>
+        <v>16.7226</v>
       </c>
       <c r="F4" t="n">
-        <v>42.50337</v>
+        <v>42.33104</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05222</v>
+        <v>0.05026</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82288</v>
+        <v>1.83598</v>
       </c>
     </row>
     <row r="5">
@@ -533,25 +534,23 @@
           <t>Unit 4</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>12,5</t>
-        </is>
+      <c r="C5" t="n">
+        <v>16.99209</v>
       </c>
       <c r="D5" t="n">
-        <v>17.26691</v>
+        <v>16.69262</v>
       </c>
       <c r="E5" t="n">
-        <v>17.09132</v>
+        <v>16.92746</v>
       </c>
       <c r="F5" t="n">
-        <v>43.01276</v>
+        <v>42.03224</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05019</v>
+        <v>0.05102</v>
       </c>
       <c r="H5" t="n">
-        <v>1.80349</v>
+        <v>1.83484</v>
       </c>
     </row>
     <row r="6">
@@ -561,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.97789</v>
+        <v>16.91628</v>
       </c>
       <c r="D6" t="n">
-        <v>16.55532</v>
+        <v>16.54239</v>
       </c>
       <c r="E6" t="n">
-        <v>16.60736</v>
+        <v>16.78744</v>
       </c>
       <c r="F6" t="n">
-        <v>42.44559</v>
+        <v>42.69191</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04922</v>
-      </c>
-      <c r="H6" t="e">
-        <v>#DIV/0!</v>
+        <v>0.05064</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.83009</v>
       </c>
     </row>
     <row r="7">
@@ -586,24 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.84555</v>
+        <v>16.69017</v>
       </c>
       <c r="D7" t="n">
-        <v>16.30286</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 16.48 </t>
-        </is>
+        <v>16.50661</v>
+      </c>
+      <c r="E7" t="n">
+        <v>16.68019</v>
       </c>
       <c r="F7" t="n">
-        <v>42.95755</v>
+        <v>43.50721</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05119</v>
+        <v>0.05005</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8336</v>
+        <v>1.79375</v>
       </c>
     </row>
     <row r="8">
@@ -613,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.65768</v>
+        <v>16.69203</v>
       </c>
       <c r="D8" t="n">
-        <v>16.63451</v>
+        <v>16.50447</v>
       </c>
       <c r="E8" t="n">
-        <v>16.7862</v>
+        <v>16.55816</v>
       </c>
       <c r="F8" t="n">
-        <v>42.16131</v>
+        <v>42.59713</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0508</v>
+        <v>0.0501</v>
       </c>
       <c r="H8" t="n">
-        <v>1.84293</v>
+        <v>1.8173</v>
       </c>
     </row>
     <row r="9">
@@ -638,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.81237</v>
+        <v>16.89538</v>
       </c>
       <c r="D9" t="n">
-        <v>16.61749</v>
+        <v>16.57841</v>
       </c>
       <c r="E9" t="n">
-        <v>16.81395</v>
+        <v>16.74718</v>
       </c>
       <c r="F9" t="n">
-        <v>42.68176</v>
+        <v>42.15209</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05077</v>
+        <v>0.04998</v>
       </c>
       <c r="H9" t="n">
-        <v>1.84053</v>
+        <v>1.83523</v>
       </c>
     </row>
     <row r="10">
@@ -663,31 +660,51 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.02286</v>
+        <v>17.17497</v>
       </c>
       <c r="D10" t="n">
-        <v>16.62985</v>
+        <v>16.61226</v>
       </c>
       <c r="E10" t="n">
-        <v>16.80906</v>
+        <v>16.69052</v>
       </c>
       <c r="F10" t="n">
-        <v>42.41613</v>
+        <v>42.71439</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05037</v>
+        <v>0.05032</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8008</v>
+        <v>1.75639</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>Dimple</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -701,14 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>via 1</t>
+          <t>Pad Pos 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>16.98937</v>
       </c>
       <c r="D12" t="n">
-        <v>1.09495</v>
+        <v>16.46906</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.72797</v>
+      </c>
+      <c r="F12" t="n">
+        <v>41.67467</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05064</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.79886</v>
       </c>
     </row>
     <row r="13">
@@ -718,10 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>17.29275</v>
       </c>
       <c r="D13" t="n">
-        <v>1.10503</v>
+        <v>16.46616</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.74222</v>
+      </c>
+      <c r="F13" t="n">
+        <v>43.02735</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.05094</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.79701</v>
       </c>
     </row>
     <row r="14">
@@ -731,10 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>16.71901</v>
       </c>
       <c r="D14" t="n">
-        <v>1.11552</v>
+        <v>16.26459</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.35773</v>
+      </c>
+      <c r="F14" t="n">
+        <v>42.25918</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05116</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.8443</v>
       </c>
     </row>
     <row r="15">
@@ -744,10 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>17.09483</v>
       </c>
       <c r="D15" t="n">
-        <v>1.10685</v>
+        <v>16.58549</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.65309</v>
+      </c>
+      <c r="F15" t="n">
+        <v>42.90947</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.04962</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.86167</v>
       </c>
     </row>
     <row r="16">
@@ -757,10 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>17.14955</v>
       </c>
       <c r="D16" t="n">
-        <v>1.13818</v>
+        <v>16.17479</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.79023</v>
+      </c>
+      <c r="F16" t="n">
+        <v>41.8872</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05081</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.84699</v>
       </c>
     </row>
     <row r="17">
@@ -770,10 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>16.70241</v>
       </c>
       <c r="D17" t="n">
-        <v>1.11804</v>
+        <v>16.26749</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.56832</v>
+      </c>
+      <c r="F17" t="n">
+        <v>42.33687</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0506</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.81989</v>
       </c>
     </row>
     <row r="18">
@@ -783,10 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>16.78793</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1185</v>
+        <v>16.3802</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.45499</v>
+      </c>
+      <c r="F18" t="n">
+        <v>42.14901</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.05128</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.8119</v>
       </c>
     </row>
     <row r="19">
@@ -796,10 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>16.87147</v>
       </c>
       <c r="D19" t="n">
-        <v>1.11433</v>
+        <v>16.70099</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.84571</v>
+      </c>
+      <c r="F19" t="n">
+        <v>42.93034</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05071</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.76652</v>
       </c>
     </row>
     <row r="20">
@@ -809,10 +922,782 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>17.27017</v>
       </c>
       <c r="D20" t="n">
-        <v>1.13483</v>
+        <v>16.76514</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.8562</v>
+      </c>
+      <c r="F20" t="n">
+        <v>42.08977</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.04973</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.81007</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SR Pad Pos 1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>15.71588</v>
+      </c>
+      <c r="D22" t="n">
+        <v>15.18548</v>
+      </c>
+      <c r="E22" t="n">
+        <v>15.51219</v>
+      </c>
+      <c r="F22" t="n">
+        <v>254.64295</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>15.73785</v>
+      </c>
+      <c r="D23" t="n">
+        <v>15.44142</v>
+      </c>
+      <c r="E23" t="n">
+        <v>15.49905</v>
+      </c>
+      <c r="F23" t="n">
+        <v>255.9587</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>15.70856</v>
+      </c>
+      <c r="D24" t="n">
+        <v>15.24481</v>
+      </c>
+      <c r="E24" t="n">
+        <v>15.53145</v>
+      </c>
+      <c r="F24" t="n">
+        <v>260.34801</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>15.82346</v>
+      </c>
+      <c r="D25" t="n">
+        <v>15.66063</v>
+      </c>
+      <c r="E25" t="n">
+        <v>15.806</v>
+      </c>
+      <c r="F25" t="n">
+        <v>251.14302</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>15.6825</v>
+      </c>
+      <c r="D26" t="n">
+        <v>15.08845</v>
+      </c>
+      <c r="E26" t="n">
+        <v>15.44722</v>
+      </c>
+      <c r="F26" t="n">
+        <v>253.4422</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>15.89697</v>
+      </c>
+      <c r="D27" t="n">
+        <v>15.56327</v>
+      </c>
+      <c r="E27" t="n">
+        <v>15.8885</v>
+      </c>
+      <c r="F27" t="n">
+        <v>257.96787</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>15.75558</v>
+      </c>
+      <c r="D28" t="n">
+        <v>15.14071</v>
+      </c>
+      <c r="E28" t="n">
+        <v>15.60839</v>
+      </c>
+      <c r="F28" t="n">
+        <v>251.44061</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>15.74461</v>
+      </c>
+      <c r="D29" t="n">
+        <v>15.31518</v>
+      </c>
+      <c r="E29" t="n">
+        <v>15.47094</v>
+      </c>
+      <c r="F29" t="n">
+        <v>255.01511</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>15.78405</v>
+      </c>
+      <c r="D30" t="n">
+        <v>15.32202</v>
+      </c>
+      <c r="E30" t="n">
+        <v>15.72188</v>
+      </c>
+      <c r="F30" t="n">
+        <v>250.55519</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trace Pos 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>16.56672</v>
+      </c>
+      <c r="D32" t="n">
+        <v>15.92928</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.14676</v>
+      </c>
+      <c r="F32" t="n">
+        <v>21.39893</v>
+      </c>
+      <c r="G32" t="n">
+        <v>34.0977</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>16.95976</v>
+      </c>
+      <c r="D33" t="n">
+        <v>15.7838</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16.36626</v>
+      </c>
+      <c r="F33" t="n">
+        <v>21.94679</v>
+      </c>
+      <c r="G33" t="n">
+        <v>34.03486</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>16.54341</v>
+      </c>
+      <c r="D34" t="n">
+        <v>16.39767</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16.52145</v>
+      </c>
+      <c r="F34" t="n">
+        <v>22.1623</v>
+      </c>
+      <c r="G34" t="n">
+        <v>33.59632</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>16.97961</v>
+      </c>
+      <c r="D35" t="n">
+        <v>15.78908</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.21427</v>
+      </c>
+      <c r="F35" t="n">
+        <v>21.63315</v>
+      </c>
+      <c r="G35" t="n">
+        <v>34.35802</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>16.67901</v>
+      </c>
+      <c r="D36" t="n">
+        <v>16.12454</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16.26242</v>
+      </c>
+      <c r="F36" t="n">
+        <v>21.20371</v>
+      </c>
+      <c r="G36" t="n">
+        <v>34.45298</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>16.79428</v>
+      </c>
+      <c r="D37" t="n">
+        <v>15.96375</v>
+      </c>
+      <c r="E37" t="n">
+        <v>16.2353</v>
+      </c>
+      <c r="F37" t="n">
+        <v>21.48113</v>
+      </c>
+      <c r="G37" t="n">
+        <v>33.91611</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>16.74031</v>
+      </c>
+      <c r="D38" t="n">
+        <v>16.1045</v>
+      </c>
+      <c r="E38" t="n">
+        <v>16.51049</v>
+      </c>
+      <c r="F38" t="n">
+        <v>21.57888</v>
+      </c>
+      <c r="G38" t="n">
+        <v>35.34307</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16.81164</v>
+      </c>
+      <c r="D39" t="n">
+        <v>16.1276</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.24105</v>
+      </c>
+      <c r="F39" t="n">
+        <v>22.02433</v>
+      </c>
+      <c r="G39" t="n">
+        <v>33.62425</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>16.47294</v>
+      </c>
+      <c r="D40" t="n">
+        <v>15.9334</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.28374</v>
+      </c>
+      <c r="F40" t="n">
+        <v>21.6303</v>
+      </c>
+      <c r="G40" t="n">
+        <v>34.37264</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Via Pos 1</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.60697</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.12164</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.60907</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.11094</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.59422</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1.10666</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.6057</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1.10879</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.6137899999999999</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1.09512</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.60761</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1.11966</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.61373</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1.0939</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.60929</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.09904</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.59876</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1.08251</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Landing Pad 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>16.76964</v>
+      </c>
+      <c r="D52" t="n">
+        <v>16.29618</v>
+      </c>
+      <c r="E52" t="n">
+        <v>16.6435</v>
+      </c>
+      <c r="F52" t="n">
+        <v>42.65566</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>17.23395</v>
+      </c>
+      <c r="D53" t="n">
+        <v>16.41027</v>
+      </c>
+      <c r="E53" t="n">
+        <v>16.87357</v>
+      </c>
+      <c r="F53" t="n">
+        <v>42.77623</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>16.6404</v>
+      </c>
+      <c r="D54" t="n">
+        <v>16.40468</v>
+      </c>
+      <c r="E54" t="n">
+        <v>16.50782</v>
+      </c>
+      <c r="F54" t="n">
+        <v>41.85614</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>16.96726</v>
+      </c>
+      <c r="D55" t="n">
+        <v>16.32916</v>
+      </c>
+      <c r="E55" t="n">
+        <v>16.61326</v>
+      </c>
+      <c r="F55" t="n">
+        <v>42.30405</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>16.65696</v>
+      </c>
+      <c r="D56" t="n">
+        <v>16.13781</v>
+      </c>
+      <c r="E56" t="n">
+        <v>16.57412</v>
+      </c>
+      <c r="F56" t="n">
+        <v>42.50523</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>16.73554</v>
+      </c>
+      <c r="D57" t="n">
+        <v>16.17903</v>
+      </c>
+      <c r="E57" t="n">
+        <v>16.45779</v>
+      </c>
+      <c r="F57" t="n">
+        <v>42.48179</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>16.68464</v>
+      </c>
+      <c r="D58" t="n">
+        <v>16.5263</v>
+      </c>
+      <c r="E58" t="n">
+        <v>16.67563</v>
+      </c>
+      <c r="F58" t="n">
+        <v>42.1206</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>17.14144</v>
+      </c>
+      <c r="D59" t="n">
+        <v>16.219</v>
+      </c>
+      <c r="E59" t="n">
+        <v>16.767</v>
+      </c>
+      <c r="F59" t="n">
+        <v>43.18225</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>17.05512</v>
+      </c>
+      <c r="D60" t="n">
+        <v>16.3772</v>
+      </c>
+      <c r="E60" t="n">
+        <v>16.7099</v>
+      </c>
+      <c r="F60" t="n">
+        <v>42.88331</v>
       </c>
     </row>
   </sheetData>
